--- a/1105/Step3_Strain_Results.xlsx
+++ b/1105/Step3_Strain_Results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="34" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -112,23 +112,23 @@
   <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.140625" customWidth="true"/>
+    <col min="1" max="1" width="3" customWidth="true"/>
     <col min="2" max="2" width="2.5703125" customWidth="true"/>
     <col min="3" max="3" width="12.140625" customWidth="true"/>
     <col min="4" max="4" width="12.5703125" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="11.85546875" customWidth="true"/>
+    <col min="6" max="6" width="12.140625" customWidth="true"/>
     <col min="7" max="7" width="12.5703125" customWidth="true"/>
-    <col min="8" max="8" width="12.7109375" customWidth="true"/>
-    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="8" max="8" width="11.85546875" customWidth="true"/>
+    <col min="9" max="9" width="12.140625" customWidth="true"/>
     <col min="10" max="10" width="12.5703125" customWidth="true"/>
     <col min="11" max="11" width="11.85546875" customWidth="true"/>
-    <col min="12" max="12" width="11.7109375" customWidth="true"/>
-    <col min="13" max="13" width="11.7109375" customWidth="true"/>
-    <col min="14" max="14" width="11.7109375" customWidth="true"/>
-    <col min="15" max="15" width="11.7109375" customWidth="true"/>
-    <col min="16" max="16" width="12.7109375" customWidth="true"/>
-    <col min="17" max="17" width="14.7109375" customWidth="true"/>
+    <col min="12" max="12" width="2" customWidth="true"/>
+    <col min="13" max="13" width="2.140625" customWidth="true"/>
+    <col min="14" max="14" width="2.28515625" customWidth="true"/>
+    <col min="15" max="15" width="8.42578125" customWidth="true"/>
+    <col min="16" max="16" width="8.28515625" customWidth="true"/>
+    <col min="17" max="17" width="8.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
